--- a/artfynd/A 17738-2026 artfynd.xlsx
+++ b/artfynd/A 17738-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133429802</v>
       </c>
       <c r="B2" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17738-2026 artfynd.xlsx
+++ b/artfynd/A 17738-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133429802</v>
       </c>
       <c r="B2" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17738-2026 artfynd.xlsx
+++ b/artfynd/A 17738-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133429802</v>
       </c>
       <c r="B2" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17738-2026 artfynd.xlsx
+++ b/artfynd/A 17738-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133429802</v>
       </c>
       <c r="B2" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17738-2026 artfynd.xlsx
+++ b/artfynd/A 17738-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133429802</v>
       </c>
       <c r="B2" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17738-2026 artfynd.xlsx
+++ b/artfynd/A 17738-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133429802</v>
+        <v>133428090</v>
       </c>
       <c r="B2" t="n">
-        <v>101388</v>
+        <v>4776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flädemo, Ög</t>
+          <t>Utmarkerna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502541</v>
+        <v>502410</v>
       </c>
       <c r="R2" t="n">
-        <v>6504680</v>
+        <v>6504584</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +788,1069 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133428121</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>502410</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6504584</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133428227</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>502398</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6504585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133428365</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502385</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6504609</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133428282</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>502385</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6504611</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133429803</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flädemo, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>502541</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6504680</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133428752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502339</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6504632</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133429066</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>502368</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6504634</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133429160</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Utmarkerna, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>502375</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6504614</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133429802</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flädemo, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>502541</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6504680</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
